--- a/nONO.xlsx
+++ b/nONO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UX433\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114A6EAC-1CBE-482A-AE16-E16967379143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E528AD-16F8-47EA-84F9-432D0E713925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="66">
   <si>
     <t>LA FRANCAISE TRESORERIE "R" ACC</t>
   </si>
@@ -231,6 +231,12 @@
   </si>
   <si>
     <t>Gastos casa Mensual</t>
+  </si>
+  <si>
+    <t>Crypto</t>
+  </si>
+  <si>
+    <t>Criptomonedas</t>
   </si>
 </sst>
 </file>
@@ -716,15 +722,15 @@
         <v>1000</v>
       </c>
       <c r="E2" s="2">
-        <f t="shared" ref="E2:E10" si="0">+D2/$D$12</f>
-        <v>0.15748031496062992</v>
+        <f t="shared" ref="E2:E11" si="0">+D2/$D$12</f>
+        <v>0.15267175572519084</v>
       </c>
       <c r="F2" s="4">
         <v>1009.89</v>
       </c>
       <c r="G2" s="2">
         <f>+F2/$F$12</f>
-        <v>0.15890291547804306</v>
+        <v>0.15523896338267193</v>
       </c>
       <c r="H2" s="2">
         <f>+(F2-D2)/D2</f>
@@ -750,17 +756,17 @@
       </c>
       <c r="E3" s="2">
         <f t="shared" si="0"/>
-        <v>0.15748031496062992</v>
+        <v>0.15267175572519084</v>
       </c>
       <c r="F3" s="4">
         <v>1008.75</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G10" si="1">+F3/$F$12</f>
-        <v>0.15872354017613396</v>
+        <f t="shared" ref="G3:G11" si="1">+F3/$F$12</f>
+        <v>0.15506372408110813</v>
       </c>
       <c r="H3" s="2">
-        <f t="shared" ref="H3:H10" si="2">+(F3-D3)/D3</f>
+        <f t="shared" ref="H3:H11" si="2">+(F3-D3)/D3</f>
         <v>8.7500000000000008E-3</v>
       </c>
       <c r="I3" s="7">
@@ -783,14 +789,14 @@
       </c>
       <c r="E4" s="2">
         <f t="shared" si="0"/>
-        <v>0.15748031496062992</v>
+        <v>0.15267175572519084</v>
       </c>
       <c r="F4" s="4">
         <v>1006.48</v>
       </c>
       <c r="G4" s="2">
         <f t="shared" si="1"/>
-        <v>0.15836636303987642</v>
+        <v>0.1547147826648364</v>
       </c>
       <c r="H4" s="2">
         <f t="shared" si="2"/>
@@ -816,14 +822,14 @@
       </c>
       <c r="E5" s="2">
         <f t="shared" si="0"/>
-        <v>0.15748031496062992</v>
+        <v>0.15267175572519084</v>
       </c>
       <c r="F5" s="4">
         <v>1002.81</v>
       </c>
       <c r="G5" s="2">
         <f t="shared" si="1"/>
-        <v>0.15778890044513397</v>
+        <v>0.15415063508874949</v>
       </c>
       <c r="H5" s="2">
         <f t="shared" si="2"/>
@@ -849,14 +855,14 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" si="0"/>
-        <v>0.14173228346456693</v>
+        <v>0.13740458015267176</v>
       </c>
       <c r="F6" s="4">
         <v>892.97</v>
       </c>
       <c r="G6" s="2">
         <f t="shared" si="1"/>
-        <v>0.14050593275943729</v>
+        <v>0.1372661746643937</v>
       </c>
       <c r="H6" s="2">
         <f t="shared" si="2"/>
@@ -882,14 +888,14 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" si="0"/>
-        <v>7.874015748031496E-2</v>
+        <v>7.6335877862595422E-2</v>
       </c>
       <c r="F7" s="4">
         <v>498.73</v>
       </c>
       <c r="G7" s="2">
         <f t="shared" si="1"/>
-        <v>7.8473547650104877E-2</v>
+        <v>7.6664120060442195E-2</v>
       </c>
       <c r="H7" s="2">
         <f t="shared" si="2"/>
@@ -915,14 +921,14 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" si="0"/>
-        <v>7.0866141732283464E-2</v>
+        <v>6.8702290076335881E-2</v>
       </c>
       <c r="F8" s="4">
         <v>438.42</v>
       </c>
       <c r="G8" s="2">
         <f t="shared" si="1"/>
-        <v>6.8983964792089875E-2</v>
+        <v>6.7393346132975901E-2</v>
       </c>
       <c r="H8" s="2">
         <f t="shared" si="2"/>
@@ -948,14 +954,14 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" si="0"/>
-        <v>3.937007874015748E-2</v>
+        <v>3.8167938931297711E-2</v>
       </c>
       <c r="F9" s="4">
         <v>249.24</v>
       </c>
       <c r="G9" s="2">
         <f t="shared" si="1"/>
-        <v>3.9217105480544863E-2</v>
+        <v>3.8312845194523312E-2</v>
       </c>
       <c r="H9" s="2">
         <f t="shared" si="2"/>
@@ -981,14 +987,14 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" si="0"/>
-        <v>3.937007874015748E-2</v>
+        <v>3.8167938931297711E-2</v>
       </c>
       <c r="F10" s="4">
         <v>248.1</v>
       </c>
       <c r="G10" s="2">
         <f t="shared" si="1"/>
-        <v>3.9037730178635772E-2</v>
+        <v>3.8137605892959531E-2</v>
       </c>
       <c r="H10" s="2">
         <f t="shared" si="2"/>
@@ -1000,15 +1006,35 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="7"/>
+      <c r="C11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="4">
+        <v>200</v>
+      </c>
+      <c r="E11" s="2">
+        <f t="shared" si="0"/>
+        <v>3.0534351145038167E-2</v>
+      </c>
+      <c r="F11" s="4">
+        <v>150</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3057802837339502E-2</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="2"/>
+        <v>-0.25</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="3"/>
+        <v>-50</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
@@ -1018,21 +1044,21 @@
       <c r="C12" s="1"/>
       <c r="D12" s="4">
         <f>+SUM(D2:D11)</f>
-        <v>6350</v>
+        <v>6550</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="4">
         <f>+SUM(F2:F11)</f>
-        <v>6355.3899999999994</v>
+        <v>6505.3899999999994</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="2">
         <f>+(F12-D12)/D12</f>
-        <v>8.4881889763770363E-4</v>
+        <v>-6.8106870229008524E-3</v>
       </c>
       <c r="I12" s="7">
         <f t="shared" si="3"/>
-        <v>5.3899999999994179</v>
+        <v>-44.610000000000582</v>
       </c>
     </row>
   </sheetData>
@@ -1051,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F45CEF-930B-4212-894F-29E2318395E6}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="61.36328125" bestFit="1" customWidth="1"/>
@@ -1089,7 +1115,7 @@
         <v>30</v>
       </c>
       <c r="D2" s="4">
-        <f>+E2*$D$16</f>
+        <f>+E2*$D$17</f>
         <v>1200</v>
       </c>
       <c r="E2" s="2">
@@ -1107,7 +1133,7 @@
         <v>31</v>
       </c>
       <c r="D3" s="4">
-        <f t="shared" ref="D3:D15" si="0">+E3*$D$16</f>
+        <f>+E3*$D$17</f>
         <v>1200</v>
       </c>
       <c r="E3" s="2">
@@ -1125,7 +1151,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" si="0"/>
+        <f>+E4*$D$17</f>
         <v>1200</v>
       </c>
       <c r="E4" s="2">
@@ -1143,7 +1169,7 @@
         <v>32</v>
       </c>
       <c r="D5" s="4">
-        <f t="shared" si="0"/>
+        <f>+E5*$D$17</f>
         <v>1200</v>
       </c>
       <c r="E5" s="2">
@@ -1161,7 +1187,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="4">
-        <f t="shared" si="0"/>
+        <f>+E6*$D$17</f>
         <v>1000</v>
       </c>
       <c r="E6" s="2">
@@ -1179,7 +1205,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="4">
-        <f t="shared" si="0"/>
+        <f>+E7*$D$17</f>
         <v>1200</v>
       </c>
       <c r="E7" s="2">
@@ -1197,7 +1223,7 @@
         <v>33</v>
       </c>
       <c r="D8" s="4">
-        <f t="shared" si="0"/>
+        <f>+E8*$D$17</f>
         <v>500</v>
       </c>
       <c r="E8" s="2">
@@ -1215,7 +1241,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="4">
-        <f t="shared" si="0"/>
+        <f>+E9*$D$17</f>
         <v>250</v>
       </c>
       <c r="E9" s="2">
@@ -1233,7 +1259,7 @@
         <v>34</v>
       </c>
       <c r="D10" s="4">
-        <f t="shared" si="0"/>
+        <f>+E10*$D$17</f>
         <v>250</v>
       </c>
       <c r="E10" s="2">
@@ -1251,11 +1277,11 @@
         <v>35</v>
       </c>
       <c r="D11" s="4">
-        <f t="shared" si="0"/>
-        <v>450</v>
+        <f>+E11*$D$17</f>
+        <v>400</v>
       </c>
       <c r="E11" s="2">
-        <v>4.4999999999999998E-2</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -1269,7 +1295,7 @@
         <v>36</v>
       </c>
       <c r="D12" s="4">
-        <f t="shared" si="0"/>
+        <f>+E12*$D$17</f>
         <v>500</v>
       </c>
       <c r="E12" s="2">
@@ -1287,11 +1313,11 @@
         <v>37</v>
       </c>
       <c r="D13" s="4">
-        <f t="shared" si="0"/>
-        <v>500</v>
+        <f>+E13*$D$17</f>
+        <v>450</v>
       </c>
       <c r="E13" s="2">
-        <v>0.05</v>
+        <v>4.4999999999999998E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -1305,7 +1331,7 @@
         <v>40</v>
       </c>
       <c r="D14" s="4">
-        <f t="shared" si="0"/>
+        <f>+E14*$D$17</f>
         <v>350.00000000000006</v>
       </c>
       <c r="E14" s="2">
@@ -1323,7 +1349,7 @@
         <v>41</v>
       </c>
       <c r="D15" s="4">
-        <f t="shared" si="0"/>
+        <f>+E15*$D$17</f>
         <v>200</v>
       </c>
       <c r="E15" s="2">
@@ -1332,15 +1358,29 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="4">
+        <v>200</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="4">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="4">
         <v>10000</v>
       </c>
-      <c r="E16" s="8">
-        <f>+SUM(E2:E15)</f>
+      <c r="E17" s="8">
+        <f>+SUM(E2:E16)</f>
         <v>1.0000000000000002</v>
       </c>
     </row>
@@ -1397,7 +1437,7 @@
       </c>
       <c r="B5" s="6">
         <f>+'informe cartera'!F12</f>
-        <v>6355.3899999999994</v>
+        <v>6505.3899999999994</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1406,7 +1446,7 @@
       </c>
       <c r="B6" s="6">
         <f>+SUM(B2:B5)</f>
-        <v>15405.39</v>
+        <v>15555.39</v>
       </c>
     </row>
   </sheetData>
@@ -1416,13 +1456,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEA8A400-DBA0-4F9C-AFEF-7B21CD1EF8FA}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -1481,6 +1522,12 @@
         <v>232</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E6">
+        <f>+B2-E2-E3-E4</f>
+        <v>577</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/nONO.xlsx
+++ b/nONO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UX433\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E528AD-16F8-47EA-84F9-432D0E713925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A31109E0-7953-47DF-9B1E-7B73BF029C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
   </bookViews>
   <sheets>
     <sheet name="informe cartera" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="67">
   <si>
     <t>LA FRANCAISE TRESORERIE "R" ACC</t>
   </si>
@@ -237,6 +237,9 @@
   </si>
   <si>
     <t>Criptomonedas</t>
+  </si>
+  <si>
+    <t>sin isin</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +1012,9 @@
       <c r="A11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="C11" s="1" t="s">
         <v>64</v>
       </c>
@@ -1115,7 +1120,7 @@
         <v>30</v>
       </c>
       <c r="D2" s="4">
-        <f>+E2*$D$17</f>
+        <f t="shared" ref="D2:D15" si="0">+E2*$D$17</f>
         <v>1200</v>
       </c>
       <c r="E2" s="2">
@@ -1133,7 +1138,7 @@
         <v>31</v>
       </c>
       <c r="D3" s="4">
-        <f>+E3*$D$17</f>
+        <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="E3" s="2">
@@ -1151,7 +1156,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="4">
-        <f>+E4*$D$17</f>
+        <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="E4" s="2">
@@ -1169,7 +1174,7 @@
         <v>32</v>
       </c>
       <c r="D5" s="4">
-        <f>+E5*$D$17</f>
+        <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="E5" s="2">
@@ -1187,7 +1192,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="4">
-        <f>+E6*$D$17</f>
+        <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="E6" s="2">
@@ -1205,7 +1210,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="4">
-        <f>+E7*$D$17</f>
+        <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="E7" s="2">
@@ -1223,7 +1228,7 @@
         <v>33</v>
       </c>
       <c r="D8" s="4">
-        <f>+E8*$D$17</f>
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="E8" s="2">
@@ -1241,7 +1246,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="4">
-        <f>+E9*$D$17</f>
+        <f t="shared" si="0"/>
         <v>250</v>
       </c>
       <c r="E9" s="2">
@@ -1259,7 +1264,7 @@
         <v>34</v>
       </c>
       <c r="D10" s="4">
-        <f>+E10*$D$17</f>
+        <f t="shared" si="0"/>
         <v>250</v>
       </c>
       <c r="E10" s="2">
@@ -1277,7 +1282,7 @@
         <v>35</v>
       </c>
       <c r="D11" s="4">
-        <f>+E11*$D$17</f>
+        <f t="shared" si="0"/>
         <v>400</v>
       </c>
       <c r="E11" s="2">
@@ -1295,7 +1300,7 @@
         <v>36</v>
       </c>
       <c r="D12" s="4">
-        <f>+E12*$D$17</f>
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="E12" s="2">
@@ -1313,7 +1318,7 @@
         <v>37</v>
       </c>
       <c r="D13" s="4">
-        <f>+E13*$D$17</f>
+        <f t="shared" si="0"/>
         <v>450</v>
       </c>
       <c r="E13" s="2">
@@ -1331,7 +1336,7 @@
         <v>40</v>
       </c>
       <c r="D14" s="4">
-        <f>+E14*$D$17</f>
+        <f t="shared" si="0"/>
         <v>350.00000000000006</v>
       </c>
       <c r="E14" s="2">
@@ -1349,7 +1354,7 @@
         <v>41</v>
       </c>
       <c r="D15" s="4">
-        <f>+E15*$D$17</f>
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="E15" s="2">

--- a/nONO.xlsx
+++ b/nONO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UX433\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A31109E0-7953-47DF-9B1E-7B73BF029C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B41974-E766-480E-822C-DF56B30DED5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
   </bookViews>
   <sheets>
     <sheet name="informe cartera" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="67">
   <si>
     <t>LA FRANCAISE TRESORERIE "R" ACC</t>
   </si>
@@ -1365,6 +1365,9 @@
       <c r="A16" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="B16" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="C16" s="1" t="s">
         <v>64</v>
       </c>

--- a/nONO.xlsx
+++ b/nONO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UX433\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B41974-E766-480E-822C-DF56B30DED5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481265B1-84F7-4CD2-8835-BC365DBC899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
   </bookViews>
   <sheets>
     <sheet name="informe cartera" sheetId="1" r:id="rId1"/>
@@ -726,14 +726,14 @@
       </c>
       <c r="E2" s="2">
         <f t="shared" ref="E2:E11" si="0">+D2/$D$12</f>
-        <v>0.15267175572519084</v>
+        <v>0.14841199168892846</v>
       </c>
       <c r="F2" s="4">
         <v>1009.89</v>
       </c>
       <c r="G2" s="2">
         <f>+F2/$F$12</f>
-        <v>0.15523896338267193</v>
+        <v>0.15305097152487199</v>
       </c>
       <c r="H2" s="2">
         <f>+(F2-D2)/D2</f>
@@ -759,14 +759,14 @@
       </c>
       <c r="E3" s="2">
         <f t="shared" si="0"/>
-        <v>0.15267175572519084</v>
+        <v>0.14841199168892846</v>
       </c>
       <c r="F3" s="4">
         <v>1008.75</v>
       </c>
       <c r="G3" s="2">
         <f t="shared" ref="G3:G11" si="1">+F3/$F$12</f>
-        <v>0.15506372408110813</v>
+        <v>0.15287820210687761</v>
       </c>
       <c r="H3" s="2">
         <f t="shared" ref="H3:H11" si="2">+(F3-D3)/D3</f>
@@ -792,14 +792,14 @@
       </c>
       <c r="E4" s="2">
         <f t="shared" si="0"/>
-        <v>0.15267175572519084</v>
+        <v>0.14841199168892846</v>
       </c>
       <c r="F4" s="4">
         <v>1006.48</v>
       </c>
       <c r="G4" s="2">
         <f t="shared" si="1"/>
-        <v>0.1547147826648364</v>
+        <v>0.1525341787920993</v>
       </c>
       <c r="H4" s="2">
         <f t="shared" si="2"/>
@@ -825,14 +825,14 @@
       </c>
       <c r="E5" s="2">
         <f t="shared" si="0"/>
-        <v>0.15267175572519084</v>
+        <v>0.14841199168892846</v>
       </c>
       <c r="F5" s="4">
         <v>1002.81</v>
       </c>
       <c r="G5" s="2">
         <f t="shared" si="1"/>
-        <v>0.15415063508874949</v>
+        <v>0.15197798250785419</v>
       </c>
       <c r="H5" s="2">
         <f t="shared" si="2"/>
@@ -858,14 +858,14 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" si="0"/>
-        <v>0.13740458015267176</v>
+        <v>0.13357079252003562</v>
       </c>
       <c r="F6" s="4">
         <v>892.97</v>
       </c>
       <c r="G6" s="2">
         <f t="shared" si="1"/>
-        <v>0.1372661746643937</v>
+        <v>0.13533149753197374</v>
       </c>
       <c r="H6" s="2">
         <f t="shared" si="2"/>
@@ -891,14 +891,14 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" si="0"/>
-        <v>7.6335877862595422E-2</v>
+        <v>7.4205995844464231E-2</v>
       </c>
       <c r="F7" s="4">
         <v>498.73</v>
       </c>
       <c r="G7" s="2">
         <f t="shared" si="1"/>
-        <v>7.6664120060442195E-2</v>
+        <v>7.5583589330124476E-2</v>
       </c>
       <c r="H7" s="2">
         <f t="shared" si="2"/>
@@ -924,14 +924,14 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" si="0"/>
-        <v>6.8702290076335881E-2</v>
+        <v>6.678539626001781E-2</v>
       </c>
       <c r="F8" s="4">
         <v>438.42</v>
       </c>
       <c r="G8" s="2">
         <f t="shared" si="1"/>
-        <v>6.7393346132975901E-2</v>
+        <v>6.6443480909737077E-2</v>
       </c>
       <c r="H8" s="2">
         <f t="shared" si="2"/>
@@ -957,14 +957,14 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" si="0"/>
-        <v>3.8167938931297711E-2</v>
+        <v>3.7102997922232116E-2</v>
       </c>
       <c r="F9" s="4">
         <v>249.24</v>
       </c>
       <c r="G9" s="2">
         <f t="shared" si="1"/>
-        <v>3.8312845194523312E-2</v>
+        <v>3.7772850649931279E-2</v>
       </c>
       <c r="H9" s="2">
         <f t="shared" si="2"/>
@@ -990,14 +990,14 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" si="0"/>
-        <v>3.8167938931297711E-2</v>
+        <v>3.7102997922232116E-2</v>
       </c>
       <c r="F10" s="4">
         <v>248.1</v>
       </c>
       <c r="G10" s="2">
         <f t="shared" si="1"/>
-        <v>3.8137605892959531E-2</v>
+        <v>3.7600081231936887E-2</v>
       </c>
       <c r="H10" s="2">
         <f t="shared" si="2"/>
@@ -1019,26 +1019,27 @@
         <v>64</v>
       </c>
       <c r="D11" s="4">
-        <v>200</v>
+        <f>+F11+145</f>
+        <v>388</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="0"/>
-        <v>3.0534351145038167E-2</v>
+        <v>5.7583852775304242E-2</v>
       </c>
       <c r="F11" s="4">
-        <v>150</v>
+        <v>243</v>
       </c>
       <c r="G11" s="2">
         <f t="shared" si="1"/>
-        <v>2.3057802837339502E-2</v>
+        <v>3.6827165414593563E-2</v>
       </c>
       <c r="H11" s="2">
         <f t="shared" si="2"/>
-        <v>-0.25</v>
+        <v>-0.37371134020618557</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" si="3"/>
-        <v>-50</v>
+        <v>-145</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -1049,21 +1050,21 @@
       <c r="C12" s="1"/>
       <c r="D12" s="4">
         <f>+SUM(D2:D11)</f>
-        <v>6550</v>
+        <v>6738</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="4">
         <f>+SUM(F2:F11)</f>
-        <v>6505.3899999999994</v>
+        <v>6598.3899999999994</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="2">
         <f>+(F12-D12)/D12</f>
-        <v>-6.8106870229008524E-3</v>
+        <v>-2.071979815969139E-2</v>
       </c>
       <c r="I12" s="7">
         <f t="shared" si="3"/>
-        <v>-44.610000000000582</v>
+        <v>-139.61000000000058</v>
       </c>
     </row>
   </sheetData>
@@ -1420,7 +1421,8 @@
         <v>42</v>
       </c>
       <c r="B2" s="6">
-        <v>7000</v>
+        <f>7528+19</f>
+        <v>7547</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1428,7 +1430,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="6">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1436,7 +1438,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="6">
-        <v>2000</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1445,7 +1447,7 @@
       </c>
       <c r="B5" s="6">
         <f>+'informe cartera'!F12</f>
-        <v>6505.3899999999994</v>
+        <v>6598.3899999999994</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1454,7 +1456,7 @@
       </c>
       <c r="B6" s="6">
         <f>+SUM(B2:B5)</f>
-        <v>15555.39</v>
+        <v>16184.39</v>
       </c>
     </row>
   </sheetData>
@@ -1499,7 +1501,7 @@
         <v>61</v>
       </c>
       <c r="E2" s="1">
-        <v>500</v>
+        <v>620</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -1533,7 +1535,7 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E6">
         <f>+B2-E2-E3-E4</f>
-        <v>577</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>

--- a/nONO.xlsx
+++ b/nONO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UX433\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481265B1-84F7-4CD2-8835-BC365DBC899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471AC71C-B005-4B24-B7B9-D5044FE822AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
   <si>
     <t>LA FRANCAISE TRESORERIE "R" ACC</t>
   </si>
@@ -240,6 +240,9 @@
   </si>
   <si>
     <t>sin isin</t>
+  </si>
+  <si>
+    <t>Gastos extras anuales</t>
   </si>
 </sst>
 </file>
@@ -322,7 +325,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -333,6 +336,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1466,7 +1470,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEA8A400-DBA0-4F9C-AFEF-7B21CD1EF8FA}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.36328125" bestFit="1" customWidth="1"/>
@@ -1501,7 +1505,7 @@
         <v>61</v>
       </c>
       <c r="E2" s="1">
-        <v>620</v>
+        <v>550</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -1532,10 +1536,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E6">
-        <f>+B2-E2-E3-E4</f>
-        <v>457</v>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D5" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="10">
+        <v>1500</v>
       </c>
     </row>
   </sheetData>

--- a/nONO.xlsx
+++ b/nONO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UX433\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471AC71C-B005-4B24-B7B9-D5044FE822AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B99F96D-5D3C-4999-8DDD-AA3C03147B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="67">
   <si>
     <t>LA FRANCAISE TRESORERIE "R" ACC</t>
   </si>
@@ -240,9 +240,6 @@
   </si>
   <si>
     <t>sin isin</t>
-  </si>
-  <si>
-    <t>Gastos extras anuales</t>
   </si>
 </sst>
 </file>
@@ -1505,7 +1502,7 @@
         <v>61</v>
       </c>
       <c r="E2" s="1">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -1537,12 +1534,8 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D5" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="10">
-        <v>1500</v>
-      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/nONO.xlsx
+++ b/nONO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UX433\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B99F96D-5D3C-4999-8DDD-AA3C03147B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86959297-78A3-48FA-8EFE-FBCBF8918E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
   <si>
     <t>LA FRANCAISE TRESORERIE "R" ACC</t>
   </si>
@@ -240,6 +240,9 @@
   </si>
   <si>
     <t>sin isin</t>
+  </si>
+  <si>
+    <t>Gastos anuales extras</t>
   </si>
 </sst>
 </file>
@@ -282,7 +285,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -316,13 +319,56 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -333,7 +379,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1519,23 +1567,27 @@
         <v>618</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B4" s="1">
         <v>2066</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="10">
         <v>232</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D5" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="12">
+        <v>1500</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/nONO.xlsx
+++ b/nONO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UX433\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86959297-78A3-48FA-8EFE-FBCBF8918E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41615A2-1A04-47B1-A9AA-655460AF4D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
   </bookViews>
@@ -1586,7 +1586,7 @@
         <v>67</v>
       </c>
       <c r="E5" s="12">
-        <v>1500</v>
+        <v>2000</v>
       </c>
     </row>
   </sheetData>

--- a/nONO.xlsx
+++ b/nONO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UX433\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41615A2-1A04-47B1-A9AA-655460AF4D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AAC3243-B81C-4FC0-9676-2C2B9485A97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
   </bookViews>
   <sheets>
     <sheet name="informe cartera" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="70">
   <si>
     <t>LA FRANCAISE TRESORERIE "R" ACC</t>
   </si>
@@ -243,6 +243,12 @@
   </si>
   <si>
     <t>Gastos anuales extras</t>
+  </si>
+  <si>
+    <t>% Renta Variable</t>
+  </si>
+  <si>
+    <t>% Renta Fija</t>
   </si>
 </sst>
 </file>
@@ -253,7 +259,7 @@
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* &quot;-&quot;??\ [$€-C0A]_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,13 +282,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="6">
@@ -368,7 +394,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -382,6 +408,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -717,9 +752,29 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="605" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{3D237F1E-B5E0-4CE5-9132-A18EC2B4C55F}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFB3D82-F7FD-4753-B5DE-B4E2F1F33D8A}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="61.36328125" bestFit="1" customWidth="1"/>
@@ -729,9 +784,10 @@
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
@@ -759,8 +815,14 @@
       <c r="I1" s="5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J1" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -793,7 +855,7 @@
         <v>9.8899999999999864</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -826,7 +888,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -859,7 +921,7 @@
         <v>6.4800000000000182</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -892,7 +954,7 @@
         <v>2.8099999999999454</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -925,7 +987,7 @@
         <v>-7.0299999999999727</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -958,7 +1020,7 @@
         <v>-1.2699999999999818</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -990,8 +1052,14 @@
         <f t="shared" si="3"/>
         <v>-11.579999999999984</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J8" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="K8" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1024,7 +1092,7 @@
         <v>-0.75999999999999091</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -1057,7 +1125,7 @@
         <v>-1.9000000000000057</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>65</v>
       </c>
@@ -1091,7 +1159,7 @@
         <v>-145</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
@@ -1117,7 +1185,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H1:I1048576">
+  <conditionalFormatting sqref="H1:I1048576 J1:K1">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -1132,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F45CEF-930B-4212-894F-29E2318395E6}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="61.36328125" bestFit="1" customWidth="1"/>
@@ -1142,7 +1210,7 @@
     <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
@@ -1158,8 +1226,14 @@
       <c r="E1" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F1" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1177,7 +1251,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1195,7 +1269,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1213,7 +1287,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1231,7 +1305,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1249,7 +1323,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1267,7 +1341,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -1284,8 +1358,16 @@
       <c r="E8" s="2">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F8" s="15">
+        <f>'informe cartera'!J8</f>
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="15">
+        <f>'informe cartera'!K8</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1303,7 +1385,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -1321,7 +1403,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -1338,8 +1420,14 @@
       <c r="E11" s="2">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F11" s="14">
+        <v>0.7</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>49</v>
       </c>
@@ -1357,7 +1445,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>52</v>
       </c>
@@ -1375,7 +1463,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>53</v>
       </c>
@@ -1393,7 +1481,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>38</v>
       </c>
@@ -1411,7 +1499,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>65</v>
       </c>

--- a/nONO.xlsx
+++ b/nONO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UX433\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AAC3243-B81C-4FC0-9676-2C2B9485A97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46CDBE2-B11F-4AE4-A277-ECDF098D5ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
   </bookViews>
   <sheets>
     <sheet name="informe cartera" sheetId="1" r:id="rId1"/>
@@ -394,7 +394,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -417,6 +417,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1185,7 +1186,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H1:I1048576 J1:K1">
+  <conditionalFormatting sqref="J1:K1 H1:I1048576">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -1208,6 +1209,8 @@
     <col min="3" max="3" width="23.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -1462,6 +1465,7 @@
       <c r="E13" s="2">
         <v>4.4999999999999998E-2</v>
       </c>
+      <c r="F13" s="16"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">

--- a/nONO.xlsx
+++ b/nONO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UX433\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/def731f4508a9d2e/Escritorio/Patrimonio seguimiento/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46CDBE2-B11F-4AE4-A277-ECDF098D5ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
   </bookViews>
   <sheets>
     <sheet name="informe cartera" sheetId="1" r:id="rId1"/>

--- a/nONO.xlsx
+++ b/nONO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/def731f4508a9d2e/Escritorio/Patrimonio seguimiento/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46CDBE2-B11F-4AE4-A277-ECDF098D5ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{F46CDBE2-B11F-4AE4-A277-ECDF098D5ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A85872EE-1F9C-42F0-8E13-C9C1F1E2DADE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{59610CB2-0EAF-4667-A94D-963F7B8D951E}"/>
   </bookViews>
   <sheets>
     <sheet name="informe cartera" sheetId="1" r:id="rId1"/>
@@ -456,6 +456,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -838,22 +842,22 @@
       </c>
       <c r="E2" s="2">
         <f t="shared" ref="E2:E11" si="0">+D2/$D$12</f>
-        <v>0.14841199168892846</v>
+        <v>0.13266118333775537</v>
       </c>
       <c r="F2" s="4">
-        <v>1009.89</v>
+        <v>1012.81</v>
       </c>
       <c r="G2" s="2">
         <f>+F2/$F$12</f>
-        <v>0.15305097152487199</v>
+        <v>0.13570338491386644</v>
       </c>
       <c r="H2" s="2">
         <f>+(F2-D2)/D2</f>
-        <v>9.8899999999999856E-3</v>
+        <v>1.2809999999999945E-2</v>
       </c>
       <c r="I2" s="7">
         <f>+F2-D2</f>
-        <v>9.8899999999999864</v>
+        <v>12.809999999999945</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
@@ -867,26 +871,26 @@
         <v>31</v>
       </c>
       <c r="D3" s="4">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E3" s="2">
         <f t="shared" si="0"/>
-        <v>0.14841199168892846</v>
+        <v>0.14592730167153092</v>
       </c>
       <c r="F3" s="4">
-        <v>1008.75</v>
+        <v>1110.78</v>
       </c>
       <c r="G3" s="2">
         <f t="shared" ref="G3:G11" si="1">+F3/$F$12</f>
-        <v>0.15287820210687761</v>
+        <v>0.14883009241084166</v>
       </c>
       <c r="H3" s="2">
         <f t="shared" ref="H3:H11" si="2">+(F3-D3)/D3</f>
-        <v>8.7500000000000008E-3</v>
+        <v>9.7999999999999754E-3</v>
       </c>
       <c r="I3" s="7">
         <f t="shared" ref="I3:I12" si="3">+F3-D3</f>
-        <v>8.75</v>
+        <v>10.779999999999973</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -900,26 +904,26 @@
         <v>31</v>
       </c>
       <c r="D4" s="4">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E4" s="2">
         <f t="shared" si="0"/>
-        <v>0.14841199168892846</v>
+        <v>0.14592730167153092</v>
       </c>
       <c r="F4" s="4">
-        <v>1006.48</v>
+        <v>1108.51</v>
       </c>
       <c r="G4" s="2">
         <f t="shared" si="1"/>
-        <v>0.1525341787920993</v>
+        <v>0.14852594189519266</v>
       </c>
       <c r="H4" s="2">
         <f t="shared" si="2"/>
-        <v>6.4800000000000179E-3</v>
+        <v>7.736363636363628E-3</v>
       </c>
       <c r="I4" s="7">
         <f t="shared" si="3"/>
-        <v>6.4800000000000182</v>
+        <v>8.5099999999999909</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
@@ -933,26 +937,26 @@
         <v>32</v>
       </c>
       <c r="D5" s="4">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E5" s="2">
         <f t="shared" si="0"/>
-        <v>0.14841199168892846</v>
+        <v>0.14592730167153092</v>
       </c>
       <c r="F5" s="4">
-        <v>1002.81</v>
+        <v>1106.04</v>
       </c>
       <c r="G5" s="2">
         <f t="shared" si="1"/>
-        <v>0.15197798250785419</v>
+        <v>0.14819499397728383</v>
       </c>
       <c r="H5" s="2">
         <f t="shared" si="2"/>
-        <v>2.8099999999999454E-3</v>
+        <v>5.4909090909090576E-3</v>
       </c>
       <c r="I5" s="7">
         <f t="shared" si="3"/>
-        <v>2.8099999999999454</v>
+        <v>6.0399999999999636</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -970,22 +974,22 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" si="0"/>
-        <v>0.13357079252003562</v>
+        <v>0.11939506500397984</v>
       </c>
       <c r="F6" s="4">
-        <v>892.97</v>
+        <v>903.31</v>
       </c>
       <c r="G6" s="2">
         <f t="shared" si="1"/>
-        <v>0.13533149753197374</v>
+        <v>0.12103180717661229</v>
       </c>
       <c r="H6" s="2">
         <f t="shared" si="2"/>
-        <v>-7.8111111111110812E-3</v>
+        <v>3.6777777777777174E-3</v>
       </c>
       <c r="I6" s="7">
         <f t="shared" si="3"/>
-        <v>-7.0299999999999727</v>
+        <v>3.3099999999999454</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -999,26 +1003,26 @@
         <v>32</v>
       </c>
       <c r="D7" s="4">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E7" s="2">
         <f t="shared" si="0"/>
-        <v>7.4205995844464231E-2</v>
+        <v>0.13266118333775537</v>
       </c>
       <c r="F7" s="4">
-        <v>498.73</v>
+        <v>999.28</v>
       </c>
       <c r="G7" s="2">
         <f t="shared" si="1"/>
-        <v>7.5583589330124476E-2</v>
+        <v>0.13389054065098926</v>
       </c>
       <c r="H7" s="2">
         <f t="shared" si="2"/>
-        <v>-2.5399999999999637E-3</v>
+        <v>-7.2000000000002726E-4</v>
       </c>
       <c r="I7" s="7">
         <f t="shared" si="3"/>
-        <v>-1.2699999999999818</v>
+        <v>-0.72000000000002728</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -1036,22 +1040,22 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" si="0"/>
-        <v>6.678539626001781E-2</v>
+        <v>5.9697532501989919E-2</v>
       </c>
       <c r="F8" s="4">
-        <v>438.42</v>
+        <v>448.48</v>
       </c>
       <c r="G8" s="2">
         <f t="shared" si="1"/>
-        <v>6.6443480909737077E-2</v>
+        <v>6.0090494827431423E-2</v>
       </c>
       <c r="H8" s="2">
         <f t="shared" si="2"/>
-        <v>-2.5733333333333299E-2</v>
+        <v>-3.3777777777777374E-3</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" si="3"/>
-        <v>-11.579999999999984</v>
+        <v>-1.5199999999999818</v>
       </c>
       <c r="J8" s="14">
         <v>0.5</v>
@@ -1075,22 +1079,22 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" si="0"/>
-        <v>3.7102997922232116E-2</v>
+        <v>3.3165295834438842E-2</v>
       </c>
       <c r="F9" s="4">
-        <v>249.24</v>
+        <v>251.74</v>
       </c>
       <c r="G9" s="2">
         <f t="shared" si="1"/>
-        <v>3.7772850649931279E-2</v>
+        <v>3.3729890224441637E-2</v>
       </c>
       <c r="H9" s="2">
         <f t="shared" si="2"/>
-        <v>-3.0399999999999637E-3</v>
+        <v>6.9600000000000365E-3</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" si="3"/>
-        <v>-0.75999999999999091</v>
+        <v>1.7400000000000091</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -1108,22 +1112,22 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" si="0"/>
-        <v>3.7102997922232116E-2</v>
+        <v>3.3165295834438842E-2</v>
       </c>
       <c r="F10" s="4">
-        <v>248.1</v>
+        <v>250.46</v>
       </c>
       <c r="G10" s="2">
         <f t="shared" si="1"/>
-        <v>3.7600081231936887E-2</v>
+        <v>3.3558386849978764E-2</v>
       </c>
       <c r="H10" s="2">
         <f t="shared" si="2"/>
-        <v>-7.6000000000000225E-3</v>
+        <v>1.8400000000000319E-3</v>
       </c>
       <c r="I10" s="7">
         <f t="shared" si="3"/>
-        <v>-1.9000000000000057</v>
+        <v>0.46000000000000796</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -1137,27 +1141,26 @@
         <v>64</v>
       </c>
       <c r="D11" s="4">
-        <f>+F11+145</f>
         <v>388</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="0"/>
-        <v>5.7583852775304242E-2</v>
+        <v>5.1472539135049088E-2</v>
       </c>
       <c r="F11" s="4">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="G11" s="2">
         <f t="shared" si="1"/>
-        <v>3.6827165414593563E-2</v>
+        <v>3.6444467073361901E-2</v>
       </c>
       <c r="H11" s="2">
         <f t="shared" si="2"/>
-        <v>-0.37371134020618557</v>
+        <v>-0.29896907216494845</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" si="3"/>
-        <v>-145</v>
+        <v>-116</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -1168,21 +1171,21 @@
       <c r="C12" s="1"/>
       <c r="D12" s="4">
         <f>+SUM(D2:D11)</f>
-        <v>6738</v>
+        <v>7538</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="4">
         <f>+SUM(F2:F11)</f>
-        <v>6598.3899999999994</v>
+        <v>7463.4100000000008</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="2">
         <f>+(F12-D12)/D12</f>
-        <v>-2.071979815969139E-2</v>
+        <v>-9.8951976651630719E-3</v>
       </c>
       <c r="I12" s="7">
         <f t="shared" si="3"/>
-        <v>-139.61000000000058</v>
+        <v>-74.589999999999236</v>
       </c>
     </row>
   </sheetData>
@@ -1562,8 +1565,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="6">
-        <f>7528+19</f>
-        <v>7547</v>
+        <v>8039</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1571,7 +1573,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="6">
-        <v>26</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1587,8 +1589,8 @@
         <v>45</v>
       </c>
       <c r="B5" s="6">
-        <f>+'informe cartera'!F12</f>
-        <v>6598.3899999999994</v>
+        <f>+'informe cartera'!F12+20.23</f>
+        <v>7483.64</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1597,7 +1599,7 @@
       </c>
       <c r="B6" s="6">
         <f>+SUM(B2:B5)</f>
-        <v>16184.39</v>
+        <v>17603.64</v>
       </c>
     </row>
   </sheetData>
